--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/02_경영지원_대외비/지출계획_2026-09-25.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/02_경영지원_대외비/지출계획_2026-09-25.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>외상매입금 1차 지급 / 9/25 주간대조 미집행 → 다음 주 이월</t>
+          <t>외상매입금 1차 지급 / 9/22 우리은행 220351에서 20,000,000 지급 확인 — 경영-20260922-004(락토프리미엄 1차)와 중복 등록분이라 취소</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/02_경영지원_대외비/지출계획_2026-09-25.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/02_경영지원_대외비/지출계획_2026-09-25.xlsx
@@ -711,17 +711,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>지급완료</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>화/수 2일치 금액</t>
+          <t>화/수 2일치 금액 / 9/25 은행 확인: 3건 분할 집행 합계 3,498,000 (9/21 우리 국민네이버 apha 2,178,000 + 에이팜건 330,000, 9/23 국민 네이버 ddi50 990,000)</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>지급완료</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>9/25 은행 확인: 9/23 국민 '네이버 에이팜건강' 330,000 집행 (계획 대비 -170,000)</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1524,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1533,7 +1538,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8305000</v>
+        <v>3630000</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1542,17 +1547,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>금주 목~차주 월까지 광고비 충전 금액</t>
+          <t>금주 목~차주 월까지 광고비 충전 금액 / 원 8,305,000 중 4,675,000은 9/23 국민 '네이버 aphar 스마트출금'으로 집행 — 잔여 3,630,000 다음 주 이월</t>
         </is>
       </c>
     </row>
